--- a/data/trans_orig/P6716-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6716-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2012</t>
+          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2012 (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>727</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>7485</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>965</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11961</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27435</t>
+          <t>28159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12062</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28097</t>
+          <t>28113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28250</t>
+          <t>28171</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50635</t>
+          <t>50059</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18582</t>
+          <t>18861</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35649</t>
+          <t>35400</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16525</t>
+          <t>15809</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32734</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38628</t>
+          <t>38942</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62275</t>
+          <t>63199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22822</t>
+          <t>21839</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41685</t>
+          <t>40915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34064</t>
+          <t>33867</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51676</t>
+          <t>53271</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61941</t>
+          <t>60573</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>88883</t>
+          <t>87694</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,39%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21644</t>
+          <t>21717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17567</t>
+          <t>17393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14838</t>
+          <t>15442</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34133</t>
+          <t>34529</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>12403</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31119</t>
+          <t>30346</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8315</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26081</t>
+          <t>26209</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27165</t>
+          <t>25974</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50904</t>
+          <t>51532</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55546</t>
+          <t>54695</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84193</t>
+          <t>86051</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37574</t>
+          <t>38294</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65217</t>
+          <t>63956</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>99916</t>
+          <t>100911</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141135</t>
+          <t>142782</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84139</t>
+          <t>84320</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119444</t>
+          <t>119159</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59405</t>
+          <t>59250</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91160</t>
+          <t>88003</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>150577</t>
+          <t>152302</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>196648</t>
+          <t>199143</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,19%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159617</t>
+          <t>156809</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197416</t>
+          <t>199217</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110180</t>
+          <t>107853</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142415</t>
+          <t>140876</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>280419</t>
+          <t>278261</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>333072</t>
+          <t>331582</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,27%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21641</t>
+          <t>22612</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14328</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>13152</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30651</t>
+          <t>30870</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13158</t>
+          <t>13001</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33197</t>
+          <t>33500</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23303</t>
+          <t>22477</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24059</t>
+          <t>25185</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49491</t>
+          <t>49084</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>65441</t>
+          <t>66202</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>98279</t>
+          <t>98453</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61274</t>
+          <t>58952</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91850</t>
+          <t>90602</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>135104</t>
+          <t>134347</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>179682</t>
+          <t>179503</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79087</t>
+          <t>79948</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>114827</t>
+          <t>114939</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44831</t>
+          <t>44105</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71343</t>
+          <t>72192</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130413</t>
+          <t>132207</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>176197</t>
+          <t>175974</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>193064</t>
+          <t>194731</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235308</t>
+          <t>236202</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116616</t>
+          <t>116797</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>150579</t>
+          <t>152137</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>319722</t>
+          <t>319115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>373691</t>
+          <t>373450</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,52%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>16759</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13411</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24186</t>
+          <t>25332</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14844</t>
+          <t>14597</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17669</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24981</t>
+          <t>24504</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43354</t>
+          <t>42808</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>74009</t>
+          <t>73407</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35439</t>
+          <t>35911</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61754</t>
+          <t>62131</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>86739</t>
+          <t>87802</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>127556</t>
+          <t>128288</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>79978</t>
+          <t>79656</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>118154</t>
+          <t>116587</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37555</t>
+          <t>37674</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64552</t>
+          <t>65434</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>124747</t>
+          <t>126057</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>171001</t>
+          <t>171916</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>175980</t>
+          <t>174694</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>216957</t>
+          <t>217989</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>98908</t>
+          <t>97078</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>129522</t>
+          <t>130829</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>286079</t>
+          <t>282703</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>336431</t>
+          <t>336172</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>12324</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14015</t>
+          <t>14865</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11923</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22172</t>
+          <t>21892</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>20775</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40237</t>
+          <t>41575</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18798</t>
+          <t>18637</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>29024</t>
+          <t>29705</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>52938</t>
+          <t>53352</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21256</t>
+          <t>20947</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41106</t>
+          <t>40960</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>36884</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>63403</t>
+          <t>64114</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>74462</t>
+          <t>74007</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>100514</t>
+          <t>99348</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>39595</t>
+          <t>39324</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>103015</t>
+          <t>100364</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>134422</t>
+          <t>132384</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>58,59%</t>
         </is>
       </c>
     </row>
@@ -4141,97 +4141,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4480,97 +4480,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>28242</t>
+          <t>28253</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>53801</t>
+          <t>53669</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>19180</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>39692</t>
+          <t>39206</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>52219</t>
+          <t>53669</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>87120</t>
+          <t>84912</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>45346</t>
+          <t>45153</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>77012</t>
+          <t>76745</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>31284</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>57676</t>
+          <t>58554</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>83702</t>
+          <t>84513</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>125829</t>
+          <t>126858</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>226886</t>
+          <t>228258</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>285938</t>
+          <t>288581</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>179451</t>
+          <t>177522</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>231325</t>
+          <t>231237</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>423210</t>
+          <t>422586</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>508088</t>
+          <t>496707</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>317329</t>
+          <t>320767</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>390213</t>
+          <t>384439</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>200005</t>
+          <t>198333</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>253605</t>
+          <t>249894</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>532829</t>
+          <t>535456</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>621080</t>
+          <t>617638</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>671257</t>
+          <t>675599</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>753581</t>
+          <t>751415</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>413153</t>
+          <t>412159</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>475492</t>
+          <t>476624</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1111012</t>
+          <t>1112674</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1208422</t>
+          <t>1208325</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6227,7 +6227,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2016</t>
+          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16455</t>
+          <t>16230</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>11905</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15031</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31994</t>
+          <t>32315</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13450</t>
+          <t>14243</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29428</t>
+          <t>29422</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33598</t>
+          <t>32871</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56689</t>
+          <t>56550</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15936</t>
+          <t>15984</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23741</t>
+          <t>22768</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40152</t>
+          <t>39784</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43099</t>
+          <t>43717</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66759</t>
+          <t>67681</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17289</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34266</t>
+          <t>33851</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20844</t>
+          <t>21478</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37863</t>
+          <t>39651</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>41886</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66323</t>
+          <t>67244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26668</t>
+          <t>27200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>13212</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>15745</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34852</t>
+          <t>35584</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14221</t>
+          <t>14761</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33196</t>
+          <t>34543</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>9592</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>25077</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26659</t>
+          <t>27608</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50948</t>
+          <t>52915</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65402</t>
+          <t>65118</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>98413</t>
+          <t>97440</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54734</t>
+          <t>53647</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82450</t>
+          <t>80629</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>128370</t>
+          <t>127257</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>168684</t>
+          <t>167982</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77570</t>
+          <t>77717</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111352</t>
+          <t>110896</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64314</t>
+          <t>64816</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92524</t>
+          <t>92996</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149694</t>
+          <t>151776</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193176</t>
+          <t>194432</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112686</t>
+          <t>111085</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>148247</t>
+          <t>148758</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,47 +7571,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>32,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>43,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>104601</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>89622</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>120466</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>38,22%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>32,74%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>104601</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>90886</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>121476</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>38,22%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>33,2%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>211606</t>
+          <t>213316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>259797</t>
+          <t>261215</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,27%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>21400</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16541</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>12179</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32104</t>
+          <t>31552</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13549</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33357</t>
+          <t>32313</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11771</t>
+          <t>11706</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28461</t>
+          <t>29876</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29868</t>
+          <t>30351</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55784</t>
+          <t>54916</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88682</t>
+          <t>88261</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>126396</t>
+          <t>126279</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56424</t>
+          <t>55535</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85811</t>
+          <t>85635</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>153823</t>
+          <t>153313</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>200685</t>
+          <t>200119</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>102875</t>
+          <t>103414</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>140753</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64415</t>
+          <t>64054</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>93985</t>
+          <t>93873</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>177907</t>
+          <t>177821</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>224264</t>
+          <t>227709</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>177592</t>
+          <t>176818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>220632</t>
+          <t>219751</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>124548</t>
+          <t>123552</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>157746</t>
+          <t>159483</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>309582</t>
+          <t>310357</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>365714</t>
+          <t>365864</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,09%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24166</t>
+          <t>23776</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23626</t>
+          <t>24099</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19441</t>
+          <t>18783</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40752</t>
+          <t>40735</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11165</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31463</t>
+          <t>31220</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25647</t>
+          <t>25313</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>23546</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49260</t>
+          <t>49105</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>54387</t>
+          <t>54478</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>86813</t>
+          <t>86178</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>45667</t>
+          <t>46170</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73635</t>
+          <t>73937</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>105833</t>
+          <t>107693</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>149905</t>
+          <t>150118</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>101576</t>
+          <t>99577</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>137031</t>
+          <t>137523</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48585</t>
+          <t>48617</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75951</t>
+          <t>74783</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>158038</t>
+          <t>158395</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>208266</t>
+          <t>205019</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>125922</t>
+          <t>128913</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>166406</t>
+          <t>167695</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>78532</t>
+          <t>79192</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>109553</t>
+          <t>110342</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>214508</t>
+          <t>215357</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>264320</t>
+          <t>266142</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12042</t>
+          <t>12804</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17277</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>23975</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21976</t>
+          <t>22206</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20532</t>
+          <t>20875</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16970</t>
+          <t>17330</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>38467</t>
+          <t>37474</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26507</t>
+          <t>26796</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>51110</t>
+          <t>50030</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>19312</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38502</t>
+          <t>37770</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>50658</t>
+          <t>50644</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>81718</t>
+          <t>80715</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>23659</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45192</t>
+          <t>45630</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>14273</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>31526</t>
+          <t>31452</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>43687</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>68830</t>
+          <t>70369</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>62799</t>
+          <t>61920</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>89089</t>
+          <t>88230</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>24862</t>
+          <t>24824</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45959</t>
+          <t>45819</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>95271</t>
+          <t>93237</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>129314</t>
+          <t>127722</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -9832,97 +9832,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>19,65%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>77,59%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>1020</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>4248</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>19,65%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>4186</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>81,84%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>4251</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -9945,97 +9945,97 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10093,62 +10093,62 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>4370</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10,12%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>4590</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>10,12%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>53,59%</t>
         </is>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>833</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9269</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -10514,97 +10514,97 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -10627,97 +10627,97 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
+      <c r="W41" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -10740,97 +10740,97 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="W42" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -10853,97 +10853,97 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -10966,97 +10966,97 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
           <t>795</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="W44" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>35206</t>
+          <t>34807</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>66203</t>
+          <t>64592</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>34963</t>
+          <t>36711</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>62750</t>
+          <t>63619</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>78021</t>
+          <t>76274</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>119675</t>
+          <t>119216</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>66251</t>
+          <t>65926</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>103824</t>
+          <t>103171</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>51937</t>
+          <t>51092</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>82652</t>
+          <t>82653</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>126360</t>
+          <t>126075</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>174615</t>
+          <t>178353</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>285785</t>
+          <t>285020</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>351781</t>
+          <t>346451</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>216962</t>
+          <t>217748</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>274523</t>
+          <t>273258</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>521464</t>
+          <t>518717</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>604264</t>
+          <t>604195</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>361713</t>
+          <t>361422</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>432494</t>
+          <t>429420</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>245893</t>
+          <t>246588</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>301454</t>
+          <t>301393</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>621082</t>
+          <t>619278</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>711192</t>
+          <t>709876</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>538483</t>
+          <t>542482</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>617169</t>
+          <t>615831</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>377272</t>
+          <t>373985</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>438026</t>
+          <t>436224</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>935274</t>
+          <t>930975</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1032868</t>
+          <t>1034850</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6716-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6716-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10696</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>958</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8827</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11841</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28159</t>
+          <t>26944</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,47 +972,47 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>14,45%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>32,52%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>19210</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>12544</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>27796</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>21,88%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>14,29%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>33,99%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19210</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12347</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28113</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>21,88%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>14,06%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28171</t>
+          <t>27422</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50059</t>
+          <t>48761</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18861</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35400</t>
+          <t>35699</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15809</t>
+          <t>15721</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>32381</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38942</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63199</t>
+          <t>63149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,0%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21839</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40915</t>
+          <t>41387</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33867</t>
+          <t>33374</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53271</t>
+          <t>52799</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60573</t>
+          <t>60457</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87694</t>
+          <t>87615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,34%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21717</t>
+          <t>22470</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17393</t>
+          <t>18048</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15442</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34529</t>
+          <t>35325</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>12389</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>31304</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26209</t>
+          <t>25820</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25974</t>
+          <t>25948</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51532</t>
+          <t>49941</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54695</t>
+          <t>54726</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86051</t>
+          <t>85948</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38294</t>
+          <t>38518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63956</t>
+          <t>65921</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>100911</t>
+          <t>99641</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>142782</t>
+          <t>141681</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84320</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119159</t>
+          <t>119259</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59250</t>
+          <t>58730</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88003</t>
+          <t>89209</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>152302</t>
+          <t>151573</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>199143</t>
+          <t>196397</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156809</t>
+          <t>159390</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>199217</t>
+          <t>199574</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107853</t>
+          <t>110311</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140876</t>
+          <t>142470</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>278261</t>
+          <t>277266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>331582</t>
+          <t>330917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,17%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22612</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15077</t>
+          <t>14434</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30870</t>
+          <t>30250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13001</t>
+          <t>13006</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33500</t>
+          <t>31376</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7263</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22477</t>
+          <t>23596</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>23674</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49084</t>
+          <t>48223</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66202</t>
+          <t>66054</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>98453</t>
+          <t>99262</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58952</t>
+          <t>59066</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90602</t>
+          <t>88635</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>134347</t>
+          <t>132463</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>179503</t>
+          <t>178250</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79948</t>
+          <t>79669</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>114939</t>
+          <t>114598</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44105</t>
+          <t>44166</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72192</t>
+          <t>72527</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>132207</t>
+          <t>130189</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>175974</t>
+          <t>176707</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194731</t>
+          <t>194081</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236202</t>
+          <t>237104</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116797</t>
+          <t>116686</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>152137</t>
+          <t>150382</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>319115</t>
+          <t>323214</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>373450</t>
+          <t>377244</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16759</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>12412</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25332</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14597</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16131</t>
+          <t>15753</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24504</t>
+          <t>23930</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42808</t>
+          <t>43061</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>73407</t>
+          <t>72851</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35911</t>
+          <t>36073</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>62131</t>
+          <t>63011</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>87802</t>
+          <t>87451</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>128288</t>
+          <t>127971</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>79656</t>
+          <t>81012</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>116587</t>
+          <t>118192</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37674</t>
+          <t>37425</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>65434</t>
+          <t>65355</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>126057</t>
+          <t>126534</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>171916</t>
+          <t>172459</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>174694</t>
+          <t>175498</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>217989</t>
+          <t>215888</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>97078</t>
+          <t>95774</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>130829</t>
+          <t>128376</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>282703</t>
+          <t>281874</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>336172</t>
+          <t>332324</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12324</t>
+          <t>11472</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14865</t>
+          <t>14021</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21892</t>
+          <t>22491</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20775</t>
+          <t>20370</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41575</t>
+          <t>41332</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18637</t>
+          <t>18393</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>29705</t>
+          <t>29622</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>53352</t>
+          <t>53002</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20947</t>
+          <t>21804</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40960</t>
+          <t>40693</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12346</t>
+          <t>12843</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28182</t>
+          <t>28819</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38046</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>64114</t>
+          <t>63814</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>74007</t>
+          <t>74952</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>99348</t>
+          <t>100650</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22650</t>
+          <t>22840</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>39324</t>
+          <t>39445</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>100364</t>
+          <t>103081</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>132384</t>
+          <t>133836</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>59,23%</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>83,64%</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>960</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,83%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>28253</t>
+          <t>28572</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>53669</t>
+          <t>53200</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>19180</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>39206</t>
+          <t>40920</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>53669</t>
+          <t>52659</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>84912</t>
+          <t>86170</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>45153</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>76745</t>
+          <t>76411</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>31361</t>
+          <t>31638</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>58554</t>
+          <t>58356</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>84513</t>
+          <t>82827</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>126858</t>
+          <t>126259</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>228258</t>
+          <t>228725</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>288581</t>
+          <t>290790</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>177522</t>
+          <t>179181</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>231237</t>
+          <t>232405</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>422586</t>
+          <t>424898</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>496707</t>
+          <t>506140</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>320767</t>
+          <t>321746</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>384439</t>
+          <t>386097</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>198333</t>
+          <t>196910</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>249894</t>
+          <t>250654</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>535456</t>
+          <t>534020</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>617638</t>
+          <t>617194</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>675599</t>
+          <t>672895</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>751415</t>
+          <t>751637</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>412159</t>
+          <t>413914</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>476624</t>
+          <t>477932</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1112674</t>
+          <t>1107715</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1208325</t>
+          <t>1209447</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>13749</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>15941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15258</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32315</t>
+          <t>32707</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>13793</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29422</t>
+          <t>29519</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32871</t>
+          <t>33650</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56550</t>
+          <t>56960</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>16361</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32199</t>
+          <t>32784</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22768</t>
+          <t>22809</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39784</t>
+          <t>40456</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43717</t>
+          <t>43431</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67681</t>
+          <t>67397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>16701</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33851</t>
+          <t>34252</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21478</t>
+          <t>21789</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39651</t>
+          <t>39267</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41886</t>
+          <t>42325</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>67244</t>
+          <t>67466</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,46%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9652</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27200</t>
+          <t>26551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13212</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15745</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35584</t>
+          <t>35298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14761</t>
+          <t>13499</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34543</t>
+          <t>33376</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>10158</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25077</t>
+          <t>24979</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27608</t>
+          <t>27861</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52915</t>
+          <t>52282</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65118</t>
+          <t>65165</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97440</t>
+          <t>95483</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53647</t>
+          <t>55212</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80629</t>
+          <t>84483</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>127257</t>
+          <t>127893</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>167982</t>
+          <t>171400</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77717</t>
+          <t>78657</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110896</t>
+          <t>112239</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64816</t>
+          <t>64428</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92996</t>
+          <t>93830</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151776</t>
+          <t>149814</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194432</t>
+          <t>193328</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111085</t>
+          <t>111571</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>148758</t>
+          <t>149751</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89622</t>
+          <t>89522</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>120466</t>
+          <t>120145</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>213316</t>
+          <t>212961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>261215</t>
+          <t>259443</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5466</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21400</t>
+          <t>21873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>17826</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12179</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31552</t>
+          <t>33576</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>13829</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32313</t>
+          <t>33117</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11706</t>
+          <t>12162</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29876</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30351</t>
+          <t>29924</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54916</t>
+          <t>54574</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88261</t>
+          <t>87789</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>126279</t>
+          <t>127367</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55535</t>
+          <t>56149</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85635</t>
+          <t>85030</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>153313</t>
+          <t>152111</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>200119</t>
+          <t>198829</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>103414</t>
+          <t>103331</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>140753</t>
+          <t>141574</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64054</t>
+          <t>63710</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>93873</t>
+          <t>93712</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>177821</t>
+          <t>176951</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>227709</t>
+          <t>224010</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>176818</t>
+          <t>175735</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>219751</t>
+          <t>221278</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>123552</t>
+          <t>123176</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>159483</t>
+          <t>157776</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>310357</t>
+          <t>315041</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>365864</t>
+          <t>369227</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23776</t>
+          <t>23976</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24099</t>
+          <t>24436</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18783</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40735</t>
+          <t>41786</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>11762</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31220</t>
+          <t>31882</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9139</t>
+          <t>8136</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25313</t>
+          <t>23960</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23546</t>
+          <t>24230</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49105</t>
+          <t>49442</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>54478</t>
+          <t>54379</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>86178</t>
+          <t>84160</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46170</t>
+          <t>44565</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73937</t>
+          <t>72105</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>107693</t>
+          <t>108814</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>150118</t>
+          <t>151700</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99577</t>
+          <t>101023</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>137523</t>
+          <t>137294</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48617</t>
+          <t>47614</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74783</t>
+          <t>76156</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>158395</t>
+          <t>158711</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>205019</t>
+          <t>205234</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,6%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>128913</t>
+          <t>128907</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>167695</t>
+          <t>166558</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>79192</t>
+          <t>77764</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>110342</t>
+          <t>109337</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>215357</t>
+          <t>216971</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>266142</t>
+          <t>267066</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>11643</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16393</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23975</t>
+          <t>22810</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22206</t>
+          <t>22672</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>6840</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20875</t>
+          <t>20941</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17330</t>
+          <t>16501</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37474</t>
+          <t>37668</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26796</t>
+          <t>27769</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50030</t>
+          <t>50423</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19312</t>
+          <t>19593</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>37770</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>50644</t>
+          <t>52138</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>80715</t>
+          <t>80356</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>23659</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45630</t>
+          <t>45540</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>14308</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>31452</t>
+          <t>32486</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>43687</t>
+          <t>43122</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>70369</t>
+          <t>70246</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>61920</t>
+          <t>62844</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>88230</t>
+          <t>89279</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>25028</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45819</t>
+          <t>45637</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>93237</t>
+          <t>92764</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>127722</t>
+          <t>127999</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,13%</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>5143</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>49,54%</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>858</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9299</t>
+          <t>9283</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,42%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>34807</t>
+          <t>36604</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>64592</t>
+          <t>68722</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>36711</t>
+          <t>35751</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>63619</t>
+          <t>62930</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>76274</t>
+          <t>78002</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>119216</t>
+          <t>118088</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>65926</t>
+          <t>65818</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>103171</t>
+          <t>102946</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>51092</t>
+          <t>50098</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>82653</t>
+          <t>82095</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>126075</t>
+          <t>126851</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>178353</t>
+          <t>172993</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>285020</t>
+          <t>283049</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>346451</t>
+          <t>351058</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>217748</t>
+          <t>214512</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>273258</t>
+          <t>271533</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>518717</t>
+          <t>522129</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>604195</t>
+          <t>606742</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>361422</t>
+          <t>359859</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>429420</t>
+          <t>427779</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>246588</t>
+          <t>242759</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>301393</t>
+          <t>301066</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>619278</t>
+          <t>623402</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>709876</t>
+          <t>709259</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>542482</t>
+          <t>541249</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>615831</t>
+          <t>618291</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>373985</t>
+          <t>374366</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>436224</t>
+          <t>439866</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,47 +11698,47 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
+          <t>42,41%</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>985952</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>933471</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>1034456</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>40,09%</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>37,95%</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
           <t>42,06%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>985952</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>930975</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>1034850</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>40,09%</t>
-        </is>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>37,85%</t>
-        </is>
-      </c>
-      <c r="W50" s="2" t="inlineStr">
-        <is>
-          <t>42,08%</t>
         </is>
       </c>
     </row>
